--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.99377222789071</v>
+        <v>4.06148798703224</v>
       </c>
       <c r="D2" t="n">
-        <v>24.72448778508502</v>
+        <v>4.017729265076317</v>
       </c>
       <c r="E2" t="n">
-        <v>11.04792531491803</v>
+        <v>1.79528786367418</v>
       </c>
       <c r="F2" t="n">
-        <v>11.0865392895144</v>
+        <v>1.80156263454609</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.30465750630164</v>
+        <v>3.462006844774016</v>
       </c>
       <c r="D3" t="n">
-        <v>21.05125575737149</v>
+        <v>3.420829060572867</v>
       </c>
       <c r="E3" t="n">
-        <v>11.04792531491803</v>
+        <v>1.79528786367418</v>
       </c>
       <c r="F3" t="n">
-        <v>11.0865392895144</v>
+        <v>1.80156263454609</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.946728311408996</v>
+        <v>0.6413433506039619</v>
       </c>
       <c r="D4" t="n">
-        <v>4.099716341053503</v>
+        <v>0.6662039054211942</v>
       </c>
       <c r="E4" t="n">
-        <v>11.04792531491803</v>
+        <v>1.79528786367418</v>
       </c>
       <c r="F4" t="n">
-        <v>11.0865392895144</v>
+        <v>1.80156263454609</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.72901583266779</v>
+        <v>3.368465072808516</v>
       </c>
       <c r="D5" t="n">
-        <v>20.7187101068527</v>
+        <v>3.366790392363565</v>
       </c>
       <c r="E5" t="n">
-        <v>11.04792531491803</v>
+        <v>1.79528786367418</v>
       </c>
       <c r="F5" t="n">
-        <v>11.0865392895144</v>
+        <v>1.80156263454609</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.98050116909594</v>
+        <v>7.30933143997809</v>
       </c>
       <c r="D6" t="n">
-        <v>45.12746477592732</v>
+        <v>7.33321302608819</v>
       </c>
       <c r="E6" t="n">
-        <v>11.04792531491803</v>
+        <v>1.79528786367418</v>
       </c>
       <c r="F6" t="n">
-        <v>11.0865392895144</v>
+        <v>1.80156263454609</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.91306826347317</v>
+        <v>5.348373592814391</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17947227060942</v>
+        <v>5.391664243974032</v>
       </c>
       <c r="E7" t="n">
-        <v>11.04792531491803</v>
+        <v>1.79528786367418</v>
       </c>
       <c r="F7" t="n">
-        <v>11.0865392895144</v>
+        <v>1.80156263454609</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.74591965388643</v>
+        <v>4.346211943756545</v>
       </c>
       <c r="D8" t="n">
-        <v>26.70901028903095</v>
+        <v>4.34021417196753</v>
       </c>
       <c r="E8" t="n">
-        <v>11.04792531491803</v>
+        <v>1.79528786367418</v>
       </c>
       <c r="F8" t="n">
-        <v>11.0865392895144</v>
+        <v>1.80156263454609</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.63037202575003</v>
+        <v>3.02743545418438</v>
       </c>
       <c r="D9" t="n">
-        <v>18.5332168056583</v>
+        <v>3.011647730919473</v>
       </c>
       <c r="E9" t="n">
-        <v>11.04792531491803</v>
+        <v>1.79528786367418</v>
       </c>
       <c r="F9" t="n">
-        <v>11.0865392895144</v>
+        <v>1.80156263454609</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
